--- a/source/9、人数基数/人数基数-6月.xlsx
+++ b/source/9、人数基数/人数基数-6月.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22400" windowHeight="10200"/>
+    <workbookView windowWidth="21550" windowHeight="10200"/>
   </bookViews>
   <sheets>
     <sheet name="人数基数模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="84">
   <si>
     <t>数据月份</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>月末在职人数</t>
+  </si>
+  <si>
+    <t>2026-06</t>
   </si>
   <si>
     <t>合肥</t>
@@ -902,7 +905,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1316,14 +1319,14 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2">
-        <v>46174</v>
+      <c r="A2" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3">
         <v>889</v>
@@ -1333,14 +1336,14 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2">
-        <v>46174</v>
+      <c r="A3" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3">
         <v>701</v>
@@ -1350,14 +1353,14 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2">
-        <v>46174</v>
+      <c r="A4" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3">
         <v>565</v>
@@ -1367,14 +1370,14 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2">
-        <v>46174</v>
+      <c r="A5" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3">
         <v>629</v>
@@ -1384,14 +1387,14 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2">
-        <v>46174</v>
+      <c r="A6" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3">
         <v>432</v>
@@ -1401,14 +1404,14 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2">
-        <v>46174</v>
+      <c r="A7" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3">
         <v>1786</v>
@@ -1418,14 +1421,14 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2">
-        <v>46174</v>
+      <c r="A8" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>1192</v>
@@ -1435,14 +1438,14 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2">
-        <v>46174</v>
+      <c r="A9" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="3">
         <v>2350</v>
@@ -1452,14 +1455,14 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2">
-        <v>46174</v>
+      <c r="A10" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3">
         <v>919</v>
@@ -1469,14 +1472,14 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="2">
-        <v>46174</v>
+      <c r="A11" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="3">
         <v>1065</v>
@@ -1486,14 +1489,14 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2">
-        <v>46174</v>
+      <c r="A12" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="3">
         <v>509</v>
@@ -1503,14 +1506,14 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="2">
-        <v>46174</v>
+      <c r="A13" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" s="3">
         <v>808</v>
@@ -1520,14 +1523,14 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="2">
-        <v>46174</v>
+      <c r="A14" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" s="3">
         <v>878</v>
@@ -1537,14 +1540,14 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="2">
-        <v>46174</v>
+      <c r="A15" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" s="3">
         <v>557</v>
@@ -1554,14 +1557,14 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2">
-        <v>46174</v>
+      <c r="A16" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="3">
         <v>1182</v>
@@ -1571,14 +1574,14 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="2">
-        <v>46174</v>
+      <c r="A17" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="3">
         <v>878</v>
@@ -1588,14 +1591,14 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="2">
-        <v>46174</v>
+      <c r="A18" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="3">
         <v>279</v>
@@ -1605,14 +1608,14 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="2">
-        <v>46174</v>
+      <c r="A19" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>936</v>
@@ -1622,14 +1625,14 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="2">
-        <v>46174</v>
+      <c r="A20" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="3">
         <v>1146</v>
@@ -1639,14 +1642,14 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="2">
-        <v>46174</v>
+      <c r="A21" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" s="3">
         <v>778</v>
@@ -1656,14 +1659,14 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="2">
-        <v>46174</v>
+      <c r="A22" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" s="3">
         <v>1019</v>
@@ -1673,14 +1676,14 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="2">
-        <v>46174</v>
+      <c r="A23" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="3">
         <v>371</v>
@@ -1690,14 +1693,14 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="2">
-        <v>46174</v>
+      <c r="A24" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" s="3">
         <v>475</v>
@@ -1707,14 +1710,14 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="2">
-        <v>46174</v>
+      <c r="A25" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="3">
         <v>1049</v>
@@ -1724,14 +1727,14 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="2">
-        <v>46174</v>
+      <c r="A26" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="3">
         <v>953</v>
@@ -1741,14 +1744,14 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="2">
-        <v>46174</v>
+      <c r="A27" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="3">
         <v>955</v>
@@ -1758,14 +1761,14 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="2">
-        <v>46174</v>
+      <c r="A28" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" s="3">
         <v>351</v>
@@ -1775,14 +1778,14 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="2">
-        <v>46174</v>
+      <c r="A29" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="3">
         <v>671</v>
@@ -1792,14 +1795,14 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="2">
-        <v>46174</v>
+      <c r="A30" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>398</v>
@@ -1809,14 +1812,14 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="2">
-        <v>46174</v>
+      <c r="A31" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" s="3">
         <v>1054</v>
@@ -1826,14 +1829,14 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="2">
-        <v>46174</v>
+      <c r="A32" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" s="3">
         <v>413</v>
@@ -1843,14 +1846,14 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="2">
-        <v>46174</v>
+      <c r="A33" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" s="3">
         <v>987</v>
@@ -1860,14 +1863,14 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="2">
-        <v>46174</v>
+      <c r="A34" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" s="3">
         <v>419</v>
@@ -1877,14 +1880,14 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="2">
-        <v>46174</v>
+      <c r="A35" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35" s="3">
         <v>872</v>
@@ -1894,14 +1897,14 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="2">
-        <v>46174</v>
+      <c r="A36" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36" s="3">
         <v>2101</v>
@@ -1911,14 +1914,14 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="2">
-        <v>46174</v>
+      <c r="A37" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" s="3">
         <v>407</v>
@@ -1928,14 +1931,14 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="2">
-        <v>46174</v>
+      <c r="A38" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" s="3">
         <v>1170</v>
@@ -1945,14 +1948,14 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="2">
-        <v>46174</v>
+      <c r="A39" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" s="3">
         <v>1539</v>
@@ -1962,14 +1965,14 @@
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="2">
-        <v>46174</v>
+      <c r="A40" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40" s="3">
         <v>826</v>
@@ -1979,14 +1982,14 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="2">
-        <v>46174</v>
+      <c r="A41" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41" s="3">
         <v>1241</v>
@@ -1996,14 +1999,14 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="2">
-        <v>46174</v>
+      <c r="A42" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D42" s="3">
         <v>407</v>
@@ -2013,14 +2016,14 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="2">
-        <v>46174</v>
+      <c r="A43" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D43" s="3">
         <v>334</v>
@@ -2030,14 +2033,14 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="2">
-        <v>46174</v>
+      <c r="A44" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D44" s="3">
         <v>1212</v>
@@ -2047,14 +2050,14 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="2">
-        <v>46174</v>
+      <c r="A45" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D45" s="3">
         <v>1424</v>
@@ -2064,14 +2067,14 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="2">
-        <v>46174</v>
+      <c r="A46" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D46" s="3">
         <v>550</v>
@@ -2081,14 +2084,14 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="2">
-        <v>46174</v>
+      <c r="A47" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" s="3">
         <v>381</v>
@@ -2098,14 +2101,14 @@
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="2">
-        <v>46174</v>
+      <c r="A48" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D48" s="3">
         <v>1077</v>
@@ -2115,14 +2118,14 @@
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="2">
-        <v>46174</v>
+      <c r="A49" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49" s="3">
         <v>351</v>
@@ -2132,14 +2135,14 @@
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="2">
-        <v>46174</v>
+      <c r="A50" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50" s="3">
         <v>503</v>
@@ -2149,14 +2152,14 @@
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="2">
-        <v>46174</v>
+      <c r="A51" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D51" s="3">
         <v>603</v>
@@ -2166,14 +2169,14 @@
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="2">
-        <v>46174</v>
+      <c r="A52" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D52" s="3">
         <v>368</v>
@@ -2183,14 +2186,14 @@
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="2">
-        <v>46174</v>
+      <c r="A53" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D53" s="3">
         <v>307</v>
@@ -2200,14 +2203,14 @@
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="2">
-        <v>46174</v>
+      <c r="A54" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D54" s="3">
         <v>771</v>
@@ -2217,14 +2220,14 @@
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="2">
-        <v>46174</v>
+      <c r="A55" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D55" s="3">
         <v>326</v>
@@ -2234,14 +2237,14 @@
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="2">
-        <v>46174</v>
+      <c r="A56" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D56" s="3">
         <v>538</v>
@@ -2251,14 +2254,14 @@
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="2">
-        <v>46174</v>
+      <c r="A57" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57" s="3">
         <v>221</v>
@@ -2268,14 +2271,14 @@
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="2">
-        <v>46174</v>
+      <c r="A58" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D58" s="3">
         <v>489</v>
@@ -2285,14 +2288,14 @@
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="2">
-        <v>46174</v>
+      <c r="A59" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D59" s="3">
         <v>554</v>
@@ -2302,14 +2305,14 @@
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="2">
-        <v>46174</v>
+      <c r="A60" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60" s="3">
         <v>1004</v>
@@ -2319,14 +2322,14 @@
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="2">
-        <v>46174</v>
+      <c r="A61" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D61" s="3">
         <v>215</v>
@@ -2336,14 +2339,14 @@
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="2">
-        <v>46174</v>
+      <c r="A62" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="D62" s="3">
         <v>617</v>
@@ -2353,14 +2356,14 @@
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="2">
-        <v>46174</v>
+      <c r="A63" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D63" s="3">
         <v>565</v>
@@ -2370,14 +2373,14 @@
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="2">
-        <v>46174</v>
+      <c r="A64" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="D64" s="3">
         <v>1282</v>
@@ -2387,14 +2390,14 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="2">
-        <v>46174</v>
+      <c r="A65" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D65" s="3">
         <v>401</v>
@@ -2404,14 +2407,14 @@
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="2">
-        <v>46174</v>
+      <c r="A66" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D66" s="3">
         <v>307</v>
@@ -2421,14 +2424,14 @@
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="2">
-        <v>46174</v>
+      <c r="A67" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="D67" s="3">
         <v>535</v>
@@ -2438,14 +2441,14 @@
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="2">
-        <v>46174</v>
+      <c r="A68" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="D68" s="3">
         <v>288</v>
@@ -2455,14 +2458,14 @@
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="2">
-        <v>46174</v>
+      <c r="A69" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D69" s="3">
         <v>1729</v>
@@ -2472,14 +2475,14 @@
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="2">
-        <v>46174</v>
+      <c r="A70" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D70" s="3">
         <v>281</v>
@@ -2489,14 +2492,14 @@
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="2">
-        <v>46174</v>
+      <c r="A71" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D71" s="3">
         <v>296</v>
@@ -2506,14 +2509,14 @@
       </c>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="2">
-        <v>46174</v>
+      <c r="A72" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D72" s="3">
         <v>146</v>
@@ -2523,14 +2526,14 @@
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="2">
-        <v>46174</v>
+      <c r="A73" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D73" s="3">
         <v>544</v>
@@ -2540,14 +2543,14 @@
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="2">
-        <v>46174</v>
+      <c r="A74" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D74" s="3">
         <v>333</v>
@@ -2557,14 +2560,14 @@
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="2">
-        <v>46174</v>
+      <c r="A75" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D75" s="3">
         <v>216</v>
@@ -2574,14 +2577,14 @@
       </c>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="2">
-        <v>46174</v>
+      <c r="A76" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D76" s="3">
         <v>219</v>
@@ -2591,14 +2594,14 @@
       </c>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="2">
-        <v>46174</v>
+      <c r="A77" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D77" s="3">
         <v>282</v>

--- a/source/9、人数基数/人数基数-6月.xlsx
+++ b/source/9、人数基数/人数基数-6月.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21550" windowHeight="10200"/>
+    <workbookView windowWidth="22400" windowHeight="10200"/>
   </bookViews>
   <sheets>
     <sheet name="人数基数模板" sheetId="1" r:id="rId1"/>
@@ -1329,10 +1329,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="3">
-        <v>889</v>
-      </c>
-      <c r="E2" s="1">
-        <v>889</v>
+        <v>894</v>
+      </c>
+      <c r="E2" s="3">
+        <v>894</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1346,10 +1346,10 @@
         <v>7</v>
       </c>
       <c r="D3" s="3">
-        <v>701</v>
-      </c>
-      <c r="E3" s="1">
-        <v>701</v>
+        <v>688</v>
+      </c>
+      <c r="E3" s="3">
+        <v>688</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1363,10 +1363,10 @@
         <v>7</v>
       </c>
       <c r="D4" s="3">
-        <v>565</v>
-      </c>
-      <c r="E4" s="1">
-        <v>565</v>
+        <v>523</v>
+      </c>
+      <c r="E4" s="3">
+        <v>523</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1380,10 +1380,10 @@
         <v>7</v>
       </c>
       <c r="D5" s="3">
-        <v>629</v>
-      </c>
-      <c r="E5" s="1">
-        <v>629</v>
+        <v>642</v>
+      </c>
+      <c r="E5" s="3">
+        <v>642</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1397,10 +1397,10 @@
         <v>7</v>
       </c>
       <c r="D6" s="3">
-        <v>432</v>
-      </c>
-      <c r="E6" s="1">
-        <v>432</v>
+        <v>434</v>
+      </c>
+      <c r="E6" s="3">
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1414,10 +1414,10 @@
         <v>7</v>
       </c>
       <c r="D7" s="3">
-        <v>1786</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1786</v>
+        <v>1771</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1771</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1431,10 +1431,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="3">
-        <v>1192</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1192</v>
+        <v>1190</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1190</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1448,10 +1448,10 @@
         <v>7</v>
       </c>
       <c r="D9" s="3">
-        <v>2350</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2350</v>
+        <v>2344</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2344</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1465,10 +1465,10 @@
         <v>7</v>
       </c>
       <c r="D10" s="3">
-        <v>919</v>
-      </c>
-      <c r="E10" s="1">
-        <v>919</v>
+        <v>894</v>
+      </c>
+      <c r="E10" s="3">
+        <v>894</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1482,10 +1482,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="3">
-        <v>1065</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1065</v>
+        <v>1084</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1084</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1499,10 +1499,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>509</v>
-      </c>
-      <c r="E12" s="1">
-        <v>509</v>
+        <v>510</v>
+      </c>
+      <c r="E12" s="3">
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1516,10 +1516,10 @@
         <v>7</v>
       </c>
       <c r="D13" s="3">
-        <v>808</v>
-      </c>
-      <c r="E13" s="1">
-        <v>808</v>
+        <v>796</v>
+      </c>
+      <c r="E13" s="3">
+        <v>796</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1533,10 +1533,10 @@
         <v>7</v>
       </c>
       <c r="D14" s="3">
-        <v>878</v>
-      </c>
-      <c r="E14" s="1">
-        <v>878</v>
+        <v>860</v>
+      </c>
+      <c r="E14" s="3">
+        <v>860</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1550,10 +1550,10 @@
         <v>7</v>
       </c>
       <c r="D15" s="3">
-        <v>557</v>
-      </c>
-      <c r="E15" s="1">
-        <v>557</v>
+        <v>540</v>
+      </c>
+      <c r="E15" s="3">
+        <v>540</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1567,10 +1567,10 @@
         <v>7</v>
       </c>
       <c r="D16" s="3">
-        <v>1182</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1182</v>
+        <v>1155</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1155</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1584,10 +1584,10 @@
         <v>7</v>
       </c>
       <c r="D17" s="3">
-        <v>878</v>
-      </c>
-      <c r="E17" s="1">
-        <v>878</v>
+        <v>852</v>
+      </c>
+      <c r="E17" s="3">
+        <v>852</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1601,10 +1601,10 @@
         <v>7</v>
       </c>
       <c r="D18" s="3">
-        <v>279</v>
-      </c>
-      <c r="E18" s="1">
-        <v>279</v>
+        <v>263</v>
+      </c>
+      <c r="E18" s="3">
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1618,10 +1618,10 @@
         <v>7</v>
       </c>
       <c r="D19" s="3">
-        <v>936</v>
-      </c>
-      <c r="E19" s="1">
-        <v>936</v>
+        <v>894</v>
+      </c>
+      <c r="E19" s="3">
+        <v>894</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1635,10 +1635,10 @@
         <v>7</v>
       </c>
       <c r="D20" s="3">
-        <v>1146</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1146</v>
+        <v>1142</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1142</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1652,10 +1652,10 @@
         <v>7</v>
       </c>
       <c r="D21" s="3">
-        <v>778</v>
-      </c>
-      <c r="E21" s="1">
-        <v>778</v>
+        <v>768</v>
+      </c>
+      <c r="E21" s="3">
+        <v>768</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1669,10 +1669,10 @@
         <v>7</v>
       </c>
       <c r="D22" s="3">
-        <v>1019</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1019</v>
+        <v>1013</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1013</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1686,10 +1686,10 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>371</v>
-      </c>
-      <c r="E23" s="1">
-        <v>371</v>
+        <v>383</v>
+      </c>
+      <c r="E23" s="3">
+        <v>383</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1703,10 +1703,10 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>475</v>
-      </c>
-      <c r="E24" s="1">
-        <v>475</v>
+        <v>472</v>
+      </c>
+      <c r="E24" s="3">
+        <v>472</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1720,10 +1720,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>1049</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1049</v>
+        <v>1045</v>
+      </c>
+      <c r="E25" s="3">
+        <v>1045</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1737,10 +1737,10 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>953</v>
-      </c>
-      <c r="E26" s="1">
-        <v>953</v>
+        <v>960</v>
+      </c>
+      <c r="E26" s="3">
+        <v>960</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1754,10 +1754,10 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>955</v>
-      </c>
-      <c r="E27" s="1">
-        <v>955</v>
+        <v>946</v>
+      </c>
+      <c r="E27" s="3">
+        <v>946</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1771,10 +1771,10 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>351</v>
-      </c>
-      <c r="E28" s="1">
-        <v>351</v>
+        <v>345</v>
+      </c>
+      <c r="E28" s="3">
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1788,10 +1788,10 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>671</v>
-      </c>
-      <c r="E29" s="1">
-        <v>671</v>
+        <v>673</v>
+      </c>
+      <c r="E29" s="3">
+        <v>673</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1805,10 +1805,10 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>398</v>
-      </c>
-      <c r="E30" s="1">
-        <v>398</v>
+        <v>405</v>
+      </c>
+      <c r="E30" s="3">
+        <v>405</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1822,10 +1822,10 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>1054</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1054</v>
+        <v>1081</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1081</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1839,10 +1839,10 @@
         <v>7</v>
       </c>
       <c r="D32" s="3">
-        <v>413</v>
-      </c>
-      <c r="E32" s="1">
-        <v>413</v>
+        <v>371</v>
+      </c>
+      <c r="E32" s="3">
+        <v>371</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1856,10 +1856,10 @@
         <v>7</v>
       </c>
       <c r="D33" s="3">
-        <v>987</v>
-      </c>
-      <c r="E33" s="1">
-        <v>987</v>
+        <v>990</v>
+      </c>
+      <c r="E33" s="3">
+        <v>990</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1873,10 +1873,10 @@
         <v>7</v>
       </c>
       <c r="D34" s="3">
-        <v>419</v>
-      </c>
-      <c r="E34" s="1">
-        <v>419</v>
+        <v>439</v>
+      </c>
+      <c r="E34" s="3">
+        <v>439</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1890,10 +1890,10 @@
         <v>7</v>
       </c>
       <c r="D35" s="3">
-        <v>872</v>
-      </c>
-      <c r="E35" s="1">
-        <v>872</v>
+        <v>887</v>
+      </c>
+      <c r="E35" s="3">
+        <v>887</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1907,10 +1907,10 @@
         <v>7</v>
       </c>
       <c r="D36" s="3">
-        <v>2101</v>
-      </c>
-      <c r="E36" s="1">
-        <v>2101</v>
+        <v>2136</v>
+      </c>
+      <c r="E36" s="3">
+        <v>2136</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1924,10 +1924,10 @@
         <v>7</v>
       </c>
       <c r="D37" s="3">
-        <v>407</v>
-      </c>
-      <c r="E37" s="1">
-        <v>407</v>
+        <v>418</v>
+      </c>
+      <c r="E37" s="3">
+        <v>418</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1941,10 +1941,10 @@
         <v>7</v>
       </c>
       <c r="D38" s="3">
-        <v>1170</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1170</v>
+        <v>1193</v>
+      </c>
+      <c r="E38" s="3">
+        <v>1193</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1958,10 +1958,10 @@
         <v>7</v>
       </c>
       <c r="D39" s="3">
-        <v>1539</v>
-      </c>
-      <c r="E39" s="1">
-        <v>1539</v>
+        <v>1465</v>
+      </c>
+      <c r="E39" s="3">
+        <v>1465</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1975,10 +1975,10 @@
         <v>7</v>
       </c>
       <c r="D40" s="3">
-        <v>826</v>
-      </c>
-      <c r="E40" s="1">
-        <v>826</v>
+        <v>930</v>
+      </c>
+      <c r="E40" s="3">
+        <v>930</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1992,10 +1992,10 @@
         <v>7</v>
       </c>
       <c r="D41" s="3">
-        <v>1241</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1241</v>
+        <v>1211</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1211</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2009,10 +2009,10 @@
         <v>7</v>
       </c>
       <c r="D42" s="3">
-        <v>407</v>
-      </c>
-      <c r="E42" s="1">
-        <v>407</v>
+        <v>406</v>
+      </c>
+      <c r="E42" s="3">
+        <v>406</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2026,10 +2026,10 @@
         <v>7</v>
       </c>
       <c r="D43" s="3">
-        <v>334</v>
-      </c>
-      <c r="E43" s="1">
-        <v>334</v>
+        <v>347</v>
+      </c>
+      <c r="E43" s="3">
+        <v>347</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2043,10 +2043,10 @@
         <v>7</v>
       </c>
       <c r="D44" s="3">
-        <v>1212</v>
-      </c>
-      <c r="E44" s="1">
-        <v>1212</v>
+        <v>1224</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1224</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2060,10 +2060,10 @@
         <v>7</v>
       </c>
       <c r="D45" s="3">
-        <v>1424</v>
-      </c>
-      <c r="E45" s="1">
-        <v>1424</v>
+        <v>1419</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1419</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2077,10 +2077,10 @@
         <v>7</v>
       </c>
       <c r="D46" s="3">
-        <v>550</v>
-      </c>
-      <c r="E46" s="1">
-        <v>550</v>
+        <v>546</v>
+      </c>
+      <c r="E46" s="3">
+        <v>546</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2094,10 +2094,10 @@
         <v>7</v>
       </c>
       <c r="D47" s="3">
-        <v>381</v>
-      </c>
-      <c r="E47" s="1">
-        <v>381</v>
+        <v>376</v>
+      </c>
+      <c r="E47" s="3">
+        <v>376</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2111,10 +2111,10 @@
         <v>7</v>
       </c>
       <c r="D48" s="3">
-        <v>1077</v>
-      </c>
-      <c r="E48" s="1">
-        <v>1077</v>
+        <v>1060</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1060</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2128,10 +2128,10 @@
         <v>7</v>
       </c>
       <c r="D49" s="3">
-        <v>351</v>
-      </c>
-      <c r="E49" s="1">
-        <v>351</v>
+        <v>350</v>
+      </c>
+      <c r="E49" s="3">
+        <v>350</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2145,10 +2145,10 @@
         <v>7</v>
       </c>
       <c r="D50" s="3">
-        <v>503</v>
-      </c>
-      <c r="E50" s="1">
-        <v>503</v>
+        <v>500</v>
+      </c>
+      <c r="E50" s="3">
+        <v>500</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2164,7 +2164,7 @@
       <c r="D51" s="3">
         <v>603</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="3">
         <v>603</v>
       </c>
     </row>
@@ -2179,10 +2179,10 @@
         <v>7</v>
       </c>
       <c r="D52" s="3">
-        <v>368</v>
-      </c>
-      <c r="E52" s="1">
-        <v>368</v>
+        <v>370</v>
+      </c>
+      <c r="E52" s="3">
+        <v>370</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2196,10 +2196,10 @@
         <v>7</v>
       </c>
       <c r="D53" s="3">
-        <v>307</v>
-      </c>
-      <c r="E53" s="1">
-        <v>307</v>
+        <v>309</v>
+      </c>
+      <c r="E53" s="3">
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2213,10 +2213,10 @@
         <v>7</v>
       </c>
       <c r="D54" s="3">
-        <v>771</v>
-      </c>
-      <c r="E54" s="1">
-        <v>771</v>
+        <v>752</v>
+      </c>
+      <c r="E54" s="3">
+        <v>752</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2230,10 +2230,10 @@
         <v>7</v>
       </c>
       <c r="D55" s="3">
-        <v>326</v>
-      </c>
-      <c r="E55" s="1">
-        <v>326</v>
+        <v>346</v>
+      </c>
+      <c r="E55" s="3">
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2247,10 +2247,10 @@
         <v>7</v>
       </c>
       <c r="D56" s="3">
-        <v>538</v>
-      </c>
-      <c r="E56" s="1">
-        <v>538</v>
+        <v>542</v>
+      </c>
+      <c r="E56" s="3">
+        <v>542</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2264,10 +2264,10 @@
         <v>7</v>
       </c>
       <c r="D57" s="3">
-        <v>221</v>
-      </c>
-      <c r="E57" s="1">
-        <v>221</v>
+        <v>220</v>
+      </c>
+      <c r="E57" s="3">
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2281,10 +2281,10 @@
         <v>7</v>
       </c>
       <c r="D58" s="3">
-        <v>489</v>
-      </c>
-      <c r="E58" s="1">
-        <v>489</v>
+        <v>531</v>
+      </c>
+      <c r="E58" s="3">
+        <v>531</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2298,10 +2298,10 @@
         <v>7</v>
       </c>
       <c r="D59" s="3">
-        <v>554</v>
-      </c>
-      <c r="E59" s="1">
-        <v>554</v>
+        <v>543</v>
+      </c>
+      <c r="E59" s="3">
+        <v>543</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2315,10 +2315,10 @@
         <v>7</v>
       </c>
       <c r="D60" s="3">
-        <v>1004</v>
-      </c>
-      <c r="E60" s="1">
-        <v>1004</v>
+        <v>1008</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1008</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2332,10 +2332,10 @@
         <v>67</v>
       </c>
       <c r="D61" s="3">
-        <v>215</v>
-      </c>
-      <c r="E61" s="1">
-        <v>215</v>
+        <v>211</v>
+      </c>
+      <c r="E61" s="3">
+        <v>211</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2349,10 +2349,10 @@
         <v>67</v>
       </c>
       <c r="D62" s="3">
-        <v>617</v>
-      </c>
-      <c r="E62" s="1">
-        <v>617</v>
+        <v>603</v>
+      </c>
+      <c r="E62" s="3">
+        <v>603</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2366,10 +2366,10 @@
         <v>67</v>
       </c>
       <c r="D63" s="3">
-        <v>565</v>
-      </c>
-      <c r="E63" s="1">
-        <v>565</v>
+        <v>551</v>
+      </c>
+      <c r="E63" s="3">
+        <v>551</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2383,10 +2383,10 @@
         <v>7</v>
       </c>
       <c r="D64" s="3">
-        <v>1282</v>
-      </c>
-      <c r="E64" s="1">
-        <v>1282</v>
+        <v>1396</v>
+      </c>
+      <c r="E64" s="3">
+        <v>1396</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2400,10 +2400,10 @@
         <v>67</v>
       </c>
       <c r="D65" s="3">
-        <v>401</v>
-      </c>
-      <c r="E65" s="1">
-        <v>401</v>
+        <v>371</v>
+      </c>
+      <c r="E65" s="3">
+        <v>371</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2417,10 +2417,10 @@
         <v>67</v>
       </c>
       <c r="D66" s="3">
-        <v>307</v>
-      </c>
-      <c r="E66" s="1">
-        <v>307</v>
+        <v>308</v>
+      </c>
+      <c r="E66" s="3">
+        <v>308</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2434,10 +2434,10 @@
         <v>7</v>
       </c>
       <c r="D67" s="3">
-        <v>535</v>
-      </c>
-      <c r="E67" s="1">
-        <v>535</v>
+        <v>510</v>
+      </c>
+      <c r="E67" s="3">
+        <v>510</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2451,10 +2451,10 @@
         <v>7</v>
       </c>
       <c r="D68" s="3">
-        <v>288</v>
-      </c>
-      <c r="E68" s="1">
-        <v>288</v>
+        <v>289</v>
+      </c>
+      <c r="E68" s="3">
+        <v>289</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2468,10 +2468,10 @@
         <v>67</v>
       </c>
       <c r="D69" s="3">
-        <v>1729</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1729</v>
+        <v>1675</v>
+      </c>
+      <c r="E69" s="3">
+        <v>1675</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2485,10 +2485,10 @@
         <v>67</v>
       </c>
       <c r="D70" s="3">
-        <v>281</v>
-      </c>
-      <c r="E70" s="1">
-        <v>281</v>
+        <v>266</v>
+      </c>
+      <c r="E70" s="3">
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2502,10 +2502,10 @@
         <v>67</v>
       </c>
       <c r="D71" s="3">
-        <v>296</v>
-      </c>
-      <c r="E71" s="1">
-        <v>296</v>
+        <v>293</v>
+      </c>
+      <c r="E71" s="3">
+        <v>293</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2519,10 +2519,10 @@
         <v>67</v>
       </c>
       <c r="D72" s="3">
-        <v>146</v>
-      </c>
-      <c r="E72" s="1">
-        <v>146</v>
+        <v>153</v>
+      </c>
+      <c r="E72" s="3">
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2536,10 +2536,10 @@
         <v>67</v>
       </c>
       <c r="D73" s="3">
-        <v>544</v>
-      </c>
-      <c r="E73" s="1">
-        <v>544</v>
+        <v>539</v>
+      </c>
+      <c r="E73" s="3">
+        <v>539</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2553,10 +2553,10 @@
         <v>67</v>
       </c>
       <c r="D74" s="3">
-        <v>333</v>
-      </c>
-      <c r="E74" s="1">
-        <v>333</v>
+        <v>339</v>
+      </c>
+      <c r="E74" s="3">
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2570,10 +2570,10 @@
         <v>67</v>
       </c>
       <c r="D75" s="3">
-        <v>216</v>
-      </c>
-      <c r="E75" s="1">
-        <v>216</v>
+        <v>220</v>
+      </c>
+      <c r="E75" s="3">
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2587,10 +2587,10 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>219</v>
-      </c>
-      <c r="E76" s="1">
-        <v>219</v>
+        <v>204</v>
+      </c>
+      <c r="E76" s="3">
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2604,10 +2604,10 @@
         <v>67</v>
       </c>
       <c r="D77" s="3">
-        <v>282</v>
-      </c>
-      <c r="E77" s="1">
-        <v>282</v>
+        <v>292</v>
+      </c>
+      <c r="E77" s="3">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
